--- a/teacher_feedback_forms/013_teacher_emotional_health_support_request_form--teacher_feedback_forms.xlsx
+++ b/teacher_feedback_forms/013_teacher_emotional_health_support_request_form--teacher_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Support Request Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How do you feel about your current emotional state?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please be honest and specific about your feelings.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>What are your concerns about your well-being?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +575,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Support Request Form</t>
+          <t>How often do you feel overwhelmed or stressed?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +598,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teacher Feedback Forms</t>
+          <t>What are your needs for support within the school environment?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +621,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>School Year</t>
+          <t>How supported do you feel by your colleagues?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +644,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>School Name</t>
+          <t>How supported do you feel by your administrators?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +667,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grade Level</t>
+          <t>How would you like to be contacted for support?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +690,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Classroom Number</t>
+          <t>Do you have any additional comments or concerns?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +713,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>School Location</t>
+          <t>What specific support requests do you have?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,358 +736,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Support Request</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Can we best support you during this time?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please be specific about your needs.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Support Request</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Teacher Name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Teacher Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>School Name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>School Location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Grade Level</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Classroom Number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>School Year</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teacher_emotional_health_support_request_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +761,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +789,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_3_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>highly_stressed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Highly Stressed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_3_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_stressed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Stressed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neither_stressed_nor_unstressed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither Stressed nor Unstressed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>highly_unstressed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Highly Unstressed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Several Times a Week</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_10_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_10_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mental_health_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mental Health Support</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_11_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>physical_health_support</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Physical Health Support</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_11_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>social_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Social Support</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_21_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>academic_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Academic Support</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>teacher_emotional_health_support_request_form_page_21_choices</t>
+          <t>teacher_emotional_health_support_request_form_page_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>very_supported</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_supported</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Somewhat Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>not_very_supported</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Very Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_5_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_at_all_supported</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not at All Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>very_supported</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Very Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>somewhat_supported</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Somewhat Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>not_very_supported</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not Very Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_at_all_supported</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not at All Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>phone_call</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>text_message</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Text Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>video_conference</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Video Conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>individualized_support</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Individualized Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>group_support</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Group Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>online_support</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Online Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_9_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>in-person_support</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>In-person Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes,_with_regular_check-ins</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes, with regular check-ins</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>yes,_with_occasional_check-ins</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yes, with occasional check-ins</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>teacher_emotional_health_support_request_form_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>no,_only_in_emergency_situations</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>No, only in emergency situations</t>
         </is>
       </c>
     </row>
